--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4192"/>
+  <dimension ref="A1:F4193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84252,19 +84252,39 @@
         <v>46276</v>
       </c>
       <c r="B4192" t="n">
-        <v>110.83</v>
+        <v>110.8300018310547</v>
       </c>
       <c r="C4192" t="n">
-        <v>112.74</v>
+        <v>112.8399963378906</v>
       </c>
       <c r="D4192" t="n">
-        <v>110.15</v>
+        <v>110.1500015258789</v>
       </c>
       <c r="E4192" t="n">
-        <v>112.6</v>
+        <v>112.5999984741211</v>
       </c>
       <c r="F4192" t="n">
         <v>3470198</v>
+      </c>
+    </row>
+    <row r="4193">
+      <c r="A4193" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B4193" t="n">
+        <v>110</v>
+      </c>
+      <c r="C4193" t="n">
+        <v>110.41</v>
+      </c>
+      <c r="D4193" t="n">
+        <v>108</v>
+      </c>
+      <c r="E4193" t="n">
+        <v>108.64</v>
+      </c>
+      <c r="F4193" t="n">
+        <v>2043775</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4193"/>
+  <dimension ref="A1:F4194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84275,16 +84275,36 @@
         <v>110</v>
       </c>
       <c r="C4193" t="n">
-        <v>110.41</v>
+        <v>110.4100036621094</v>
       </c>
       <c r="D4193" t="n">
         <v>108</v>
       </c>
       <c r="E4193" t="n">
-        <v>108.64</v>
+        <v>108.6399993896484</v>
       </c>
       <c r="F4193" t="n">
         <v>2043775</v>
+      </c>
+    </row>
+    <row r="4194">
+      <c r="A4194" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B4194" t="n">
+        <v>110</v>
+      </c>
+      <c r="C4194" t="n">
+        <v>110.69</v>
+      </c>
+      <c r="D4194" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="E4194" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="F4194" t="n">
+        <v>1637704</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4194"/>
+  <dimension ref="A1:F4195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84295,16 +84295,36 @@
         <v>110</v>
       </c>
       <c r="C4194" t="n">
-        <v>110.69</v>
+        <v>110.6900024414062</v>
       </c>
       <c r="D4194" t="n">
-        <v>109.15</v>
+        <v>109.1500015258789</v>
       </c>
       <c r="E4194" t="n">
-        <v>110.1</v>
+        <v>110.0999984741211</v>
       </c>
       <c r="F4194" t="n">
         <v>1637704</v>
+      </c>
+    </row>
+    <row r="4195">
+      <c r="A4195" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B4195" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="C4195" t="n">
+        <v>111.34</v>
+      </c>
+      <c r="D4195" t="n">
+        <v>109.03</v>
+      </c>
+      <c r="E4195" t="n">
+        <v>109.69</v>
+      </c>
+      <c r="F4195" t="n">
+        <v>2335663</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4195"/>
+  <dimension ref="A1:F4196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84312,19 +84312,39 @@
         <v>46281</v>
       </c>
       <c r="B4195" t="n">
-        <v>110.3</v>
+        <v>110.3000030517578</v>
       </c>
       <c r="C4195" t="n">
-        <v>111.34</v>
+        <v>111.3000030517578</v>
       </c>
       <c r="D4195" t="n">
-        <v>109.03</v>
+        <v>109.0299987792969</v>
       </c>
       <c r="E4195" t="n">
-        <v>109.69</v>
+        <v>109.6900024414062</v>
       </c>
       <c r="F4195" t="n">
         <v>2335663</v>
+      </c>
+    </row>
+    <row r="4196">
+      <c r="A4196" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B4196" t="n">
+        <v>109.69</v>
+      </c>
+      <c r="C4196" t="n">
+        <v>111.44</v>
+      </c>
+      <c r="D4196" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="E4196" t="n">
+        <v>111.31</v>
+      </c>
+      <c r="F4196" t="n">
+        <v>2218206</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4196"/>
+  <dimension ref="A1:F4197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84331,20 +84331,32 @@
       <c r="A4196" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B4196" t="n">
+      <c r="B4196" t="inlineStr"/>
+      <c r="C4196" t="inlineStr"/>
+      <c r="D4196" t="inlineStr"/>
+      <c r="E4196" t="inlineStr"/>
+      <c r="F4196" t="n">
+        <v>3530868</v>
+      </c>
+    </row>
+    <row r="4197">
+      <c r="A4197" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B4197" t="n">
         <v>109.69</v>
       </c>
-      <c r="C4196" t="n">
-        <v>111.44</v>
-      </c>
-      <c r="D4196" t="n">
-        <v>108.35</v>
-      </c>
-      <c r="E4196" t="n">
-        <v>111.31</v>
-      </c>
-      <c r="F4196" t="n">
-        <v>2218206</v>
+      <c r="C4197" t="n">
+        <v>109.87</v>
+      </c>
+      <c r="D4197" t="n">
+        <v>108.51</v>
+      </c>
+      <c r="E4197" t="n">
+        <v>108.96</v>
+      </c>
+      <c r="F4197" t="n">
+        <v>3536131</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4197"/>
+  <dimension ref="A1:F4198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84331,12 +84331,20 @@
       <c r="A4196" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B4196" t="inlineStr"/>
-      <c r="C4196" t="inlineStr"/>
-      <c r="D4196" t="inlineStr"/>
-      <c r="E4196" t="inlineStr"/>
+      <c r="B4196" t="n">
+        <v>109.6900024414062</v>
+      </c>
+      <c r="C4196" t="n">
+        <v>111.4400024414062</v>
+      </c>
+      <c r="D4196" t="n">
+        <v>108.3899993896484</v>
+      </c>
+      <c r="E4196" t="n">
+        <v>111.3099975585938</v>
+      </c>
       <c r="F4196" t="n">
-        <v>3530868</v>
+        <v>2218206</v>
       </c>
     </row>
     <row r="4197">
@@ -84344,19 +84352,39 @@
         <v>46283</v>
       </c>
       <c r="B4197" t="n">
-        <v>109.69</v>
+        <v>109.6900024414062</v>
       </c>
       <c r="C4197" t="n">
-        <v>109.87</v>
+        <v>109.870002746582</v>
       </c>
       <c r="D4197" t="n">
-        <v>108.51</v>
+        <v>108.5100021362305</v>
       </c>
       <c r="E4197" t="n">
-        <v>108.96</v>
+        <v>108.9599990844727</v>
       </c>
       <c r="F4197" t="n">
-        <v>3536131</v>
+        <v>3539931</v>
+      </c>
+    </row>
+    <row r="4198">
+      <c r="A4198" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B4198" t="n">
+        <v>112</v>
+      </c>
+      <c r="C4198" t="n">
+        <v>112.43</v>
+      </c>
+      <c r="D4198" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="E4198" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="F4198" t="n">
+        <v>5127932</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4198"/>
+  <dimension ref="A1:F4199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84375,16 +84375,36 @@
         <v>112</v>
       </c>
       <c r="C4198" t="n">
-        <v>112.43</v>
+        <v>112.4300003051758</v>
       </c>
       <c r="D4198" t="n">
-        <v>110.2</v>
+        <v>110.1999969482422</v>
       </c>
       <c r="E4198" t="n">
-        <v>110.2</v>
+        <v>110.1999969482422</v>
       </c>
       <c r="F4198" t="n">
         <v>5127932</v>
+      </c>
+    </row>
+    <row r="4199">
+      <c r="A4199" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4199" t="n">
+        <v>112.04</v>
+      </c>
+      <c r="C4199" t="n">
+        <v>112.23</v>
+      </c>
+      <c r="D4199" t="n">
+        <v>110.61</v>
+      </c>
+      <c r="E4199" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="F4199" t="n">
+        <v>3579770</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4199"/>
+  <dimension ref="A1:F4200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84392,19 +84392,39 @@
         <v>46287</v>
       </c>
       <c r="B4199" t="n">
-        <v>112.04</v>
+        <v>112.0400009155273</v>
       </c>
       <c r="C4199" t="n">
-        <v>112.23</v>
+        <v>112.2300033569336</v>
       </c>
       <c r="D4199" t="n">
-        <v>110.61</v>
+        <v>110.6100006103516</v>
       </c>
       <c r="E4199" t="n">
-        <v>111.35</v>
+        <v>111.3499984741211</v>
       </c>
       <c r="F4199" t="n">
         <v>3579770</v>
+      </c>
+    </row>
+    <row r="4200">
+      <c r="A4200" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B4200" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="C4200" t="n">
+        <v>113.03</v>
+      </c>
+      <c r="D4200" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="E4200" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F4200" t="n">
+        <v>2584049</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4200"/>
+  <dimension ref="A1:F4201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84412,19 +84412,39 @@
         <v>46288</v>
       </c>
       <c r="B4200" t="n">
-        <v>110.7</v>
+        <v>110.6999969482422</v>
       </c>
       <c r="C4200" t="n">
-        <v>113.03</v>
+        <v>113.0299987792969</v>
       </c>
       <c r="D4200" t="n">
-        <v>110.7</v>
+        <v>110.6999969482422</v>
       </c>
       <c r="E4200" t="n">
         <v>111.5</v>
       </c>
       <c r="F4200" t="n">
         <v>2584049</v>
+      </c>
+    </row>
+    <row r="4201">
+      <c r="A4201" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B4201" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="C4201" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="D4201" t="n">
+        <v>109.62</v>
+      </c>
+      <c r="E4201" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="F4201" t="n">
+        <v>1838718</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4201"/>
+  <dimension ref="A1:F4202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84432,19 +84432,39 @@
         <v>46289</v>
       </c>
       <c r="B4201" t="n">
-        <v>109.95</v>
+        <v>109.9499969482422</v>
       </c>
       <c r="C4201" t="n">
-        <v>111.4</v>
+        <v>111.4000015258789</v>
       </c>
       <c r="D4201" t="n">
-        <v>109.62</v>
+        <v>109.620002746582</v>
       </c>
       <c r="E4201" t="n">
-        <v>111.4</v>
+        <v>111.4000015258789</v>
       </c>
       <c r="F4201" t="n">
         <v>1838718</v>
+      </c>
+    </row>
+    <row r="4202">
+      <c r="A4202" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B4202" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="C4202" t="n">
+        <v>110.82</v>
+      </c>
+      <c r="D4202" t="n">
+        <v>109.02</v>
+      </c>
+      <c r="E4202" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="F4202" t="n">
+        <v>2869450</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4202"/>
+  <dimension ref="A1:F4203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84452,19 +84452,39 @@
         <v>46290</v>
       </c>
       <c r="B4202" t="n">
-        <v>110.45</v>
+        <v>110.4499969482422</v>
       </c>
       <c r="C4202" t="n">
-        <v>110.82</v>
+        <v>110.8199996948242</v>
       </c>
       <c r="D4202" t="n">
-        <v>109.02</v>
+        <v>109.0500030517578</v>
       </c>
       <c r="E4202" t="n">
         <v>109.75</v>
       </c>
       <c r="F4202" t="n">
         <v>2869450</v>
+      </c>
+    </row>
+    <row r="4203">
+      <c r="A4203" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B4203" t="n">
+        <v>109</v>
+      </c>
+      <c r="C4203" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="D4203" t="n">
+        <v>108.57</v>
+      </c>
+      <c r="E4203" t="n">
+        <v>109.76</v>
+      </c>
+      <c r="F4203" t="n">
+        <v>3498622</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4203"/>
+  <dimension ref="A1:F4204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84475,16 +84475,36 @@
         <v>109</v>
       </c>
       <c r="C4203" t="n">
-        <v>110.15</v>
+        <v>110.129997253418</v>
       </c>
       <c r="D4203" t="n">
-        <v>108.57</v>
+        <v>108.5699996948242</v>
       </c>
       <c r="E4203" t="n">
-        <v>109.76</v>
+        <v>109.7600021362305</v>
       </c>
       <c r="F4203" t="n">
         <v>3498622</v>
+      </c>
+    </row>
+    <row r="4204">
+      <c r="A4204" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4204" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="C4204" t="n">
+        <v>110</v>
+      </c>
+      <c r="D4204" t="n">
+        <v>108.03</v>
+      </c>
+      <c r="E4204" t="n">
+        <v>108.86</v>
+      </c>
+      <c r="F4204" t="n">
+        <v>2059431</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4204"/>
+  <dimension ref="A1:F4205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84492,19 +84492,39 @@
         <v>46294</v>
       </c>
       <c r="B4204" t="n">
-        <v>109.65</v>
+        <v>109.6500015258789</v>
       </c>
       <c r="C4204" t="n">
         <v>110</v>
       </c>
       <c r="D4204" t="n">
-        <v>108.03</v>
+        <v>108.0299987792969</v>
       </c>
       <c r="E4204" t="n">
-        <v>108.86</v>
+        <v>108.8600006103516</v>
       </c>
       <c r="F4204" t="n">
         <v>2059431</v>
+      </c>
+    </row>
+    <row r="4205">
+      <c r="A4205" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B4205" t="n">
+        <v>111.93</v>
+      </c>
+      <c r="C4205" t="n">
+        <v>112.74</v>
+      </c>
+      <c r="D4205" t="n">
+        <v>110.08</v>
+      </c>
+      <c r="E4205" t="n">
+        <v>112</v>
+      </c>
+      <c r="F4205" t="n">
+        <v>4999973</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4205"/>
+  <dimension ref="A1:F4206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84512,19 +84512,39 @@
         <v>46295</v>
       </c>
       <c r="B4205" t="n">
-        <v>111.93</v>
+        <v>111.9300003051758</v>
       </c>
       <c r="C4205" t="n">
-        <v>112.74</v>
+        <v>112.7399978637695</v>
       </c>
       <c r="D4205" t="n">
-        <v>110.08</v>
+        <v>110.0800018310547</v>
       </c>
       <c r="E4205" t="n">
         <v>112</v>
       </c>
       <c r="F4205" t="n">
         <v>4999973</v>
+      </c>
+    </row>
+    <row r="4206">
+      <c r="A4206" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4206" t="n">
+        <v>113.09</v>
+      </c>
+      <c r="C4206" t="n">
+        <v>113.41</v>
+      </c>
+      <c r="D4206" t="n">
+        <v>111.18</v>
+      </c>
+      <c r="E4206" t="n">
+        <v>111.93</v>
+      </c>
+      <c r="F4206" t="n">
+        <v>3720626</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4206"/>
+  <dimension ref="A1:F4207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84532,19 +84532,39 @@
         <v>46296</v>
       </c>
       <c r="B4206" t="n">
-        <v>113.09</v>
+        <v>113.0199966430664</v>
       </c>
       <c r="C4206" t="n">
-        <v>113.41</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="D4206" t="n">
-        <v>111.18</v>
+        <v>110.0800018310547</v>
       </c>
       <c r="E4206" t="n">
-        <v>111.93</v>
+        <v>112</v>
       </c>
       <c r="F4206" t="n">
         <v>3720626</v>
+      </c>
+    </row>
+    <row r="4207">
+      <c r="A4207" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B4207" t="n">
+        <v>116.34</v>
+      </c>
+      <c r="C4207" t="n">
+        <v>116.57</v>
+      </c>
+      <c r="D4207" t="n">
+        <v>112.81</v>
+      </c>
+      <c r="E4207" t="n">
+        <v>115</v>
+      </c>
+      <c r="F4207" t="n">
+        <v>8976858</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4207"/>
+  <dimension ref="A1:F4208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84552,19 +84552,39 @@
         <v>46297</v>
       </c>
       <c r="B4207" t="n">
-        <v>116.34</v>
+        <v>116.3399963378906</v>
       </c>
       <c r="C4207" t="n">
-        <v>116.57</v>
+        <v>116.5599975585938</v>
       </c>
       <c r="D4207" t="n">
-        <v>112.81</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="E4207" t="n">
         <v>115</v>
       </c>
       <c r="F4207" t="n">
         <v>8976858</v>
+      </c>
+    </row>
+    <row r="4208">
+      <c r="A4208" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B4208" t="n">
+        <v>127.19</v>
+      </c>
+      <c r="C4208" t="n">
+        <v>130.98</v>
+      </c>
+      <c r="D4208" t="n">
+        <v>126.47</v>
+      </c>
+      <c r="E4208" t="n">
+        <v>130</v>
+      </c>
+      <c r="F4208" t="n">
+        <v>14015653</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4208"/>
+  <dimension ref="A1:F4209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83984,7 +83984,7 @@
         <v>100.25</v>
       </c>
       <c r="F4178" t="n">
-        <v>3646974</v>
+        <v>3646368</v>
       </c>
     </row>
     <row r="4179">
@@ -84572,19 +84572,39 @@
         <v>46300</v>
       </c>
       <c r="B4208" t="n">
-        <v>127.19</v>
+        <v>127.1900024414062</v>
       </c>
       <c r="C4208" t="n">
-        <v>130.98</v>
+        <v>130.9799957275391</v>
       </c>
       <c r="D4208" t="n">
-        <v>126.47</v>
+        <v>126.4700012207031</v>
       </c>
       <c r="E4208" t="n">
         <v>130</v>
       </c>
       <c r="F4208" t="n">
         <v>14015653</v>
+      </c>
+    </row>
+    <row r="4209">
+      <c r="A4209" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B4209" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="C4209" t="n">
+        <v>130.44</v>
+      </c>
+      <c r="D4209" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="E4209" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="F4209" t="n">
+        <v>9342417</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4209"/>
+  <dimension ref="A1:F4210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84592,19 +84592,39 @@
         <v>46301</v>
       </c>
       <c r="B4209" t="n">
-        <v>128.6</v>
+        <v>128.6000061035156</v>
       </c>
       <c r="C4209" t="n">
-        <v>130.44</v>
+        <v>130.4400024414062</v>
       </c>
       <c r="D4209" t="n">
-        <v>127.3</v>
+        <v>127.3000030517578</v>
       </c>
       <c r="E4209" t="n">
-        <v>127.3</v>
+        <v>127.3000030517578</v>
       </c>
       <c r="F4209" t="n">
         <v>9342417</v>
+      </c>
+    </row>
+    <row r="4210">
+      <c r="A4210" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B4210" t="n">
+        <v>130.2</v>
+      </c>
+      <c r="C4210" t="n">
+        <v>131.66</v>
+      </c>
+      <c r="D4210" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="E4210" t="n">
+        <v>129.16</v>
+      </c>
+      <c r="F4210" t="n">
+        <v>12526448</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4210"/>
+  <dimension ref="A1:F4211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84612,19 +84612,39 @@
         <v>46302</v>
       </c>
       <c r="B4210" t="n">
-        <v>130.2</v>
+        <v>130.1999969482422</v>
       </c>
       <c r="C4210" t="n">
-        <v>131.66</v>
+        <v>131.6600036621094</v>
       </c>
       <c r="D4210" t="n">
-        <v>128.75</v>
+        <v>128.7700042724609</v>
       </c>
       <c r="E4210" t="n">
-        <v>129.16</v>
+        <v>129.1600036621094</v>
       </c>
       <c r="F4210" t="n">
         <v>12526448</v>
+      </c>
+    </row>
+    <row r="4211">
+      <c r="A4211" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B4211" t="n">
+        <v>134.39</v>
+      </c>
+      <c r="C4211" t="n">
+        <v>135.38</v>
+      </c>
+      <c r="D4211" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="E4211" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="F4211" t="n">
+        <v>22304916</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4211"/>
+  <dimension ref="A1:F4212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84632,19 +84632,39 @@
         <v>46303</v>
       </c>
       <c r="B4211" t="n">
-        <v>134.39</v>
+        <v>134.3899993896484</v>
       </c>
       <c r="C4211" t="n">
-        <v>135.38</v>
+        <v>135</v>
       </c>
       <c r="D4211" t="n">
         <v>129.5</v>
       </c>
       <c r="E4211" t="n">
-        <v>129.9</v>
+        <v>129.8999938964844</v>
       </c>
       <c r="F4211" t="n">
         <v>22304916</v>
+      </c>
+    </row>
+    <row r="4212">
+      <c r="A4212" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B4212" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="C4212" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="D4212" t="n">
+        <v>135.72</v>
+      </c>
+      <c r="E4212" t="n">
+        <v>135.85</v>
+      </c>
+      <c r="F4212" t="n">
+        <v>19272702</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -84652,16 +84652,16 @@
         <v>46304</v>
       </c>
       <c r="B4212" t="n">
-        <v>139.8</v>
+        <v>139.8000030517578</v>
       </c>
       <c r="C4212" t="n">
-        <v>139.8</v>
+        <v>139.8000030517578</v>
       </c>
       <c r="D4212" t="n">
-        <v>135.72</v>
+        <v>135.7200012207031</v>
       </c>
       <c r="E4212" t="n">
-        <v>135.85</v>
+        <v>135.8500061035156</v>
       </c>
       <c r="F4212" t="n">
         <v>19272702</v>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4212"/>
+  <dimension ref="A1:F4213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84667,6 +84667,26 @@
         <v>19272702</v>
       </c>
     </row>
+    <row r="4213">
+      <c r="A4213" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B4213" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="C4213" t="n">
+        <v>138.38</v>
+      </c>
+      <c r="D4213" t="n">
+        <v>134.24</v>
+      </c>
+      <c r="E4213" t="n">
+        <v>138.22</v>
+      </c>
+      <c r="F4213" t="n">
+        <v>9573770</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4213"/>
+  <dimension ref="A1:F4214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84672,19 +84672,39 @@
         <v>46308</v>
       </c>
       <c r="B4213" t="n">
-        <v>134.99</v>
+        <v>134.9900054931641</v>
       </c>
       <c r="C4213" t="n">
-        <v>138.38</v>
+        <v>138.3800048828125</v>
       </c>
       <c r="D4213" t="n">
-        <v>134.24</v>
+        <v>134.2400054931641</v>
       </c>
       <c r="E4213" t="n">
-        <v>138.22</v>
+        <v>138.2200012207031</v>
       </c>
       <c r="F4213" t="n">
         <v>9573770</v>
+      </c>
+    </row>
+    <row r="4214">
+      <c r="A4214" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4214" t="n">
+        <v>133.38</v>
+      </c>
+      <c r="C4214" t="n">
+        <v>134.3</v>
+      </c>
+      <c r="D4214" t="n">
+        <v>129.79</v>
+      </c>
+      <c r="E4214" t="n">
+        <v>132.73</v>
+      </c>
+      <c r="F4214" t="n">
+        <v>13197254</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4214"/>
+  <dimension ref="A1:F4215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84692,19 +84692,39 @@
         <v>46309</v>
       </c>
       <c r="B4214" t="n">
-        <v>133.38</v>
+        <v>133.3800048828125</v>
       </c>
       <c r="C4214" t="n">
-        <v>134.3</v>
+        <v>134.2899932861328</v>
       </c>
       <c r="D4214" t="n">
-        <v>129.79</v>
+        <v>129.7899932861328</v>
       </c>
       <c r="E4214" t="n">
-        <v>132.73</v>
+        <v>132.7299957275391</v>
       </c>
       <c r="F4214" t="n">
         <v>13197254</v>
+      </c>
+    </row>
+    <row r="4215">
+      <c r="A4215" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4215" t="n">
+        <v>130.83</v>
+      </c>
+      <c r="C4215" t="n">
+        <v>134.06</v>
+      </c>
+      <c r="D4215" t="n">
+        <v>129.78</v>
+      </c>
+      <c r="E4215" t="n">
+        <v>131.84</v>
+      </c>
+      <c r="F4215" t="n">
+        <v>8444648</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4215"/>
+  <dimension ref="A1:F4216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84712,19 +84712,39 @@
         <v>46310</v>
       </c>
       <c r="B4215" t="n">
-        <v>130.83</v>
+        <v>130.8300018310547</v>
       </c>
       <c r="C4215" t="n">
-        <v>134.06</v>
+        <v>134.0599975585938</v>
       </c>
       <c r="D4215" t="n">
-        <v>129.78</v>
+        <v>129.6999969482422</v>
       </c>
       <c r="E4215" t="n">
-        <v>131.84</v>
+        <v>131.8399963378906</v>
       </c>
       <c r="F4215" t="n">
         <v>8444648</v>
+      </c>
+    </row>
+    <row r="4216">
+      <c r="A4216" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4216" t="n">
+        <v>131</v>
+      </c>
+      <c r="C4216" t="n">
+        <v>132.68</v>
+      </c>
+      <c r="D4216" t="n">
+        <v>123</v>
+      </c>
+      <c r="E4216" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="F4216" t="n">
+        <v>6928665</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4216"/>
+  <dimension ref="A1:F4217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84735,16 +84735,36 @@
         <v>131</v>
       </c>
       <c r="C4216" t="n">
-        <v>132.68</v>
+        <v>132.6799926757812</v>
       </c>
       <c r="D4216" t="n">
-        <v>123</v>
+        <v>123.4499969482422</v>
       </c>
       <c r="E4216" t="n">
-        <v>132.2</v>
+        <v>132.1999969482422</v>
       </c>
       <c r="F4216" t="n">
         <v>6928665</v>
+      </c>
+    </row>
+    <row r="4217">
+      <c r="A4217" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4217" t="n">
+        <v>134.79</v>
+      </c>
+      <c r="C4217" t="n">
+        <v>134.79</v>
+      </c>
+      <c r="D4217" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="E4217" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="F4217" t="n">
+        <v>8093099</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4217"/>
+  <dimension ref="A1:F4218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84752,19 +84752,39 @@
         <v>46314</v>
       </c>
       <c r="B4217" t="n">
-        <v>134.79</v>
+        <v>134.7899932861328</v>
       </c>
       <c r="C4217" t="n">
-        <v>134.79</v>
+        <v>134.7899932861328</v>
       </c>
       <c r="D4217" t="n">
-        <v>131.9</v>
+        <v>131.8999938964844</v>
       </c>
       <c r="E4217" t="n">
-        <v>131.9</v>
+        <v>131.8999938964844</v>
       </c>
       <c r="F4217" t="n">
         <v>8093099</v>
+      </c>
+    </row>
+    <row r="4218">
+      <c r="A4218" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4218" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="C4218" t="n">
+        <v>138.93</v>
+      </c>
+      <c r="D4218" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="E4218" t="n">
+        <v>138.71</v>
+      </c>
+      <c r="F4218" t="n">
+        <v>12811426</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4218"/>
+  <dimension ref="A1:F4219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84772,19 +84772,39 @@
         <v>46315</v>
       </c>
       <c r="B4218" t="n">
-        <v>138.8</v>
+        <v>138.8000030517578</v>
       </c>
       <c r="C4218" t="n">
-        <v>138.93</v>
+        <v>138.9299926757812</v>
       </c>
       <c r="D4218" t="n">
-        <v>136.6</v>
+        <v>136.6000061035156</v>
       </c>
       <c r="E4218" t="n">
-        <v>138.71</v>
+        <v>138.7100067138672</v>
       </c>
       <c r="F4218" t="n">
         <v>12811426</v>
+      </c>
+    </row>
+    <row r="4219">
+      <c r="A4219" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B4219" t="n">
+        <v>136.76</v>
+      </c>
+      <c r="C4219" t="n">
+        <v>140.2</v>
+      </c>
+      <c r="D4219" t="n">
+        <v>135.64</v>
+      </c>
+      <c r="E4219" t="n">
+        <v>138.93</v>
+      </c>
+      <c r="F4219" t="n">
+        <v>9047823</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4219"/>
+  <dimension ref="A1:F4220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84792,19 +84792,39 @@
         <v>46316</v>
       </c>
       <c r="B4219" t="n">
-        <v>136.76</v>
+        <v>136.7599945068359</v>
       </c>
       <c r="C4219" t="n">
-        <v>140.2</v>
+        <v>140.1999969482422</v>
       </c>
       <c r="D4219" t="n">
-        <v>135.64</v>
+        <v>135.6399993896484</v>
       </c>
       <c r="E4219" t="n">
-        <v>138.93</v>
+        <v>138.9299926757812</v>
       </c>
       <c r="F4219" t="n">
         <v>9047823</v>
+      </c>
+    </row>
+    <row r="4220">
+      <c r="A4220" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B4220" t="n">
+        <v>134.7</v>
+      </c>
+      <c r="C4220" t="n">
+        <v>137.07</v>
+      </c>
+      <c r="D4220" t="n">
+        <v>133.59</v>
+      </c>
+      <c r="E4220" t="n">
+        <v>136.76</v>
+      </c>
+      <c r="F4220" t="n">
+        <v>12764646</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4220"/>
+  <dimension ref="A1:F4221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84812,19 +84812,39 @@
         <v>46317</v>
       </c>
       <c r="B4220" t="n">
-        <v>134.7</v>
+        <v>134.6999969482422</v>
       </c>
       <c r="C4220" t="n">
-        <v>137.07</v>
+        <v>137.0700073242188</v>
       </c>
       <c r="D4220" t="n">
-        <v>133.59</v>
+        <v>133.5899963378906</v>
       </c>
       <c r="E4220" t="n">
-        <v>136.76</v>
+        <v>136.7599945068359</v>
       </c>
       <c r="F4220" t="n">
         <v>12764646</v>
+      </c>
+    </row>
+    <row r="4221">
+      <c r="A4221" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B4221" t="n">
+        <v>137.16</v>
+      </c>
+      <c r="C4221" t="n">
+        <v>137.66</v>
+      </c>
+      <c r="D4221" t="n">
+        <v>133.59</v>
+      </c>
+      <c r="E4221" t="n">
+        <v>135</v>
+      </c>
+      <c r="F4221" t="n">
+        <v>11815512</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4221"/>
+  <dimension ref="A1:F4222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84832,19 +84832,39 @@
         <v>46318</v>
       </c>
       <c r="B4221" t="n">
-        <v>137.16</v>
+        <v>137.1600036621094</v>
       </c>
       <c r="C4221" t="n">
-        <v>137.66</v>
+        <v>137.6600036621094</v>
       </c>
       <c r="D4221" t="n">
-        <v>133.59</v>
+        <v>133.5899963378906</v>
       </c>
       <c r="E4221" t="n">
         <v>135</v>
       </c>
       <c r="F4221" t="n">
         <v>11815512</v>
+      </c>
+    </row>
+    <row r="4222">
+      <c r="A4222" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4222" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="C4222" t="n">
+        <v>103</v>
+      </c>
+      <c r="D4222" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="E4222" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="F4222" t="n">
+        <v>31356307</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4222"/>
+  <dimension ref="A1:F4223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83984,7 +83984,7 @@
         <v>100.25</v>
       </c>
       <c r="F4178" t="n">
-        <v>3646368</v>
+        <v>3646974</v>
       </c>
     </row>
     <row r="4179">
@@ -84852,19 +84852,39 @@
         <v>46321</v>
       </c>
       <c r="B4222" t="n">
-        <v>98.81</v>
+        <v>98.80999755859375</v>
       </c>
       <c r="C4222" t="n">
         <v>103</v>
       </c>
       <c r="D4222" t="n">
-        <v>68.84</v>
+        <v>68.80999755859375</v>
       </c>
       <c r="E4222" t="n">
-        <v>98.81</v>
+        <v>68.80999755859375</v>
       </c>
       <c r="F4222" t="n">
-        <v>31356307</v>
+        <v>31782323</v>
+      </c>
+    </row>
+    <row r="4223">
+      <c r="A4223" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4223" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="C4223" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="D4223" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="E4223" t="n">
+        <v>100.73</v>
+      </c>
+      <c r="F4223" t="n">
+        <v>27621854</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4223"/>
+  <dimension ref="A1:F4224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84872,19 +84872,39 @@
         <v>46322</v>
       </c>
       <c r="B4223" t="n">
-        <v>99.09999999999999</v>
+        <v>99.09999847412109</v>
       </c>
       <c r="C4223" t="n">
         <v>103.25</v>
       </c>
       <c r="D4223" t="n">
-        <v>98.8</v>
+        <v>98.80000305175781</v>
       </c>
       <c r="E4223" t="n">
-        <v>100.73</v>
+        <v>100.7300033569336</v>
       </c>
       <c r="F4223" t="n">
         <v>27621854</v>
+      </c>
+    </row>
+    <row r="4224">
+      <c r="A4224" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B4224" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="C4224" t="n">
+        <v>99</v>
+      </c>
+      <c r="D4224" t="n">
+        <v>94</v>
+      </c>
+      <c r="E4224" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="F4224" t="n">
+        <v>10017477</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4224"/>
+  <dimension ref="A1:F4225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84892,7 +84892,7 @@
         <v>46323</v>
       </c>
       <c r="B4224" t="n">
-        <v>95.06</v>
+        <v>95.05999755859375</v>
       </c>
       <c r="C4224" t="n">
         <v>99</v>
@@ -84901,10 +84901,30 @@
         <v>94</v>
       </c>
       <c r="E4224" t="n">
-        <v>98.76000000000001</v>
+        <v>98.76000213623047</v>
       </c>
       <c r="F4224" t="n">
         <v>10017477</v>
+      </c>
+    </row>
+    <row r="4225">
+      <c r="A4225" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B4225" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="C4225" t="n">
+        <v>96.37</v>
+      </c>
+      <c r="D4225" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E4225" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="F4225" t="n">
+        <v>7280860</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4225"/>
+  <dimension ref="A1:F4226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84915,16 +84915,36 @@
         <v>92.5</v>
       </c>
       <c r="C4225" t="n">
-        <v>96.37</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D4225" t="n">
         <v>92.5</v>
       </c>
       <c r="E4225" t="n">
-        <v>94.98999999999999</v>
+        <v>94.98999786376953</v>
       </c>
       <c r="F4225" t="n">
         <v>7280860</v>
+      </c>
+    </row>
+    <row r="4226">
+      <c r="A4226" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B4226" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="C4226" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="D4226" t="n">
+        <v>90.39</v>
+      </c>
+      <c r="E4226" t="n">
+        <v>92</v>
+      </c>
+      <c r="F4226" t="n">
+        <v>5175574</v>
       </c>
     </row>
   </sheetData>
